--- a/Team-Data/2012-13/3-24-2012-13.xlsx
+++ b/Team-Data/2012-13/3-24-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" t="n">
         <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -688,19 +755,19 @@
         <v>8.9</v>
       </c>
       <c r="M2" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="N2" t="n">
         <v>0.379</v>
       </c>
       <c r="O2" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="P2" t="n">
         <v>19.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.709</v>
+        <v>0.708</v>
       </c>
       <c r="R2" t="n">
         <v>9.199999999999999</v>
@@ -712,7 +779,7 @@
         <v>40.8</v>
       </c>
       <c r="U2" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="V2" t="n">
         <v>15.1</v>
@@ -727,7 +794,7 @@
         <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA2" t="n">
         <v>18.7</v>
@@ -736,10 +803,10 @@
         <v>97.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
         <v>11</v>
@@ -805,7 +872,7 @@
         <v>6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
         <v>14</v>
@@ -936,25 +1003,25 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
       </c>
       <c r="AK3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL3" t="n">
         <v>24</v>
       </c>
       <c r="AM3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP3" t="n">
         <v>20</v>
@@ -972,7 +1039,7 @@
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>12</v>
@@ -984,7 +1051,7 @@
         <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>27</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.586</v>
+        <v>0.58</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1049,22 +1116,22 @@
         <v>0.445</v>
       </c>
       <c r="L4" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M4" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O4" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P4" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.74</v>
+        <v>0.737</v>
       </c>
       <c r="R4" t="n">
         <v>12.5</v>
@@ -1085,7 +1152,7 @@
         <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y4" t="n">
         <v>4.8</v>
@@ -1097,13 +1164,13 @@
         <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC4" t="n">
         <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
@@ -1136,13 +1203,13 @@
         <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>6</v>
@@ -1163,10 +1230,10 @@
         <v>23</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
         <v>2</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -1207,46 +1274,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="n">
         <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>0.229</v>
+        <v>0.232</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="J5" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.419</v>
+        <v>0.42</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
       </c>
       <c r="M5" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.337</v>
+        <v>0.34</v>
       </c>
       <c r="O5" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P5" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.747</v>
+        <v>0.748</v>
       </c>
       <c r="R5" t="n">
         <v>11.3</v>
@@ -1258,7 +1325,7 @@
         <v>40.2</v>
       </c>
       <c r="U5" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="V5" t="n">
         <v>13.8</v>
@@ -1276,16 +1343,16 @@
         <v>19.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.9</v>
+        <v>-9.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
@@ -1297,7 +1364,7 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
@@ -1312,13 +1379,13 @@
         <v>26</v>
       </c>
       <c r="AM5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN5" t="n">
         <v>26</v>
       </c>
-      <c r="AN5" t="n">
-        <v>27</v>
-      </c>
       <c r="AO5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="n">
         <v>4</v>
@@ -1330,7 +1397,7 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -1389,61 +1456,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
         <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.551</v>
+        <v>0.544</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J6" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M6" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O6" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P6" t="n">
         <v>21.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R6" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="T6" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U6" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V6" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1455,19 +1522,19 @@
         <v>5.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA6" t="n">
         <v>19.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1485,10 +1552,10 @@
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1497,10 +1564,10 @@
         <v>29</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
         <v>21</v>
@@ -1512,10 +1579,10 @@
         <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
@@ -1527,7 +1594,7 @@
         <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1667,7 +1734,7 @@
         <v>19</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK7" t="n">
         <v>28</v>
@@ -1682,16 +1749,16 @@
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>15</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
@@ -1715,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
         <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>0.486</v>
+        <v>0.478</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
@@ -1771,28 +1838,28 @@
         <v>38.7</v>
       </c>
       <c r="J8" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M8" t="n">
         <v>20.1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.376</v>
+        <v>0.374</v>
       </c>
       <c r="O8" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="P8" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.794</v>
+        <v>0.792</v>
       </c>
       <c r="R8" t="n">
         <v>9.300000000000001</v>
@@ -1801,19 +1868,19 @@
         <v>32.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U8" t="n">
         <v>23.1</v>
       </c>
       <c r="V8" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W8" t="n">
         <v>7.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y8" t="n">
         <v>4.1</v>
@@ -1822,25 +1889,25 @@
         <v>20.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.7</v>
+        <v>101.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.6</v>
+        <v>-0.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1849,10 +1916,10 @@
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL8" t="n">
         <v>10</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
         <v>22</v>
@@ -1891,7 +1958,7 @@
         <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
         <v>23</v>
@@ -2216,7 +2283,7 @@
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>23</v>
@@ -2228,7 +2295,7 @@
         <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
         <v>14</v>
@@ -2249,13 +2316,13 @@
         <v>23</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>26</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
         <v>10</v>
@@ -2389,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>10</v>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2440,13 +2507,13 @@
         <v>26</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -2481,46 +2548,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
         <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J12" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L12" t="n">
         <v>10.7</v>
       </c>
       <c r="M12" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="N12" t="n">
         <v>0.37</v>
       </c>
       <c r="O12" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P12" t="n">
         <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R12" t="n">
         <v>10.9</v>
@@ -2544,22 +2611,22 @@
         <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA12" t="n">
         <v>20.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.4</v>
+        <v>106.5</v>
       </c>
       <c r="AC12" t="n">
         <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2592,7 +2659,7 @@
         <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP12" t="n">
         <v>5</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2783,7 +2850,7 @@
         <v>18</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS13" t="n">
         <v>2</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2965,7 +3032,7 @@
         <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
         <v>20</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3120,7 +3187,7 @@
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>22</v>
@@ -3165,10 +3232,10 @@
         <v>24</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
@@ -3299,7 +3366,7 @@
         <v>6</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI16" t="n">
         <v>20</v>
@@ -3323,7 +3390,7 @@
         <v>21</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
         <v>9</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.797</v>
+        <v>0.794</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
@@ -3415,34 +3482,34 @@
         <v>0.496</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N17" t="n">
-        <v>0.389</v>
+        <v>0.388</v>
       </c>
       <c r="O17" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
         <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T17" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="U17" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V17" t="n">
         <v>13.6</v>
@@ -3451,13 +3518,13 @@
         <v>8.9</v>
       </c>
       <c r="X17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
         <v>20.7</v>
@@ -3466,10 +3533,10 @@
         <v>103.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3496,7 +3563,7 @@
         <v>7</v>
       </c>
       <c r="AM17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN17" t="n">
         <v>2</v>
@@ -3514,7 +3581,7 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3544,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -3573,55 +3640,55 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
       </c>
       <c r="I18" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J18" t="n">
-        <v>87.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="K18" t="n">
         <v>0.436</v>
       </c>
       <c r="L18" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M18" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O18" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P18" t="n">
         <v>21.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.737</v>
+        <v>0.739</v>
       </c>
       <c r="R18" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S18" t="n">
         <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="U18" t="n">
         <v>22.9</v>
@@ -3630,7 +3697,7 @@
         <v>14.1</v>
       </c>
       <c r="W18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X18" t="n">
         <v>7.1</v>
@@ -3639,25 +3706,25 @@
         <v>4.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB18" t="n">
         <v>98.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
         <v>16</v>
@@ -3672,7 +3739,7 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
         <v>17</v>
@@ -3681,19 +3748,19 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>19</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS18" t="n">
         <v>13</v>
@@ -3720,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" t="n">
         <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>0.353</v>
+        <v>0.358</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
@@ -3773,43 +3840,43 @@
         <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L19" t="n">
         <v>5.3</v>
       </c>
       <c r="M19" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.294</v>
+        <v>0.292</v>
       </c>
       <c r="O19" t="n">
         <v>18.4</v>
       </c>
       <c r="P19" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q19" t="n">
         <v>0.732</v>
       </c>
       <c r="R19" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S19" t="n">
         <v>30.3</v>
       </c>
       <c r="T19" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U19" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W19" t="n">
         <v>8.1</v>
@@ -3824,16 +3891,16 @@
         <v>18.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB19" t="n">
         <v>94.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE19" t="n">
         <v>24</v>
@@ -3848,13 +3915,13 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ19" t="n">
         <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL19" t="n">
         <v>28</v>
@@ -3875,7 +3942,7 @@
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS19" t="n">
         <v>17</v>
@@ -3887,7 +3954,7 @@
         <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
         <v>13</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -4015,13 +4082,13 @@
         <v>-3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
         <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
         <v>25</v>
@@ -4057,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4078,10 +4145,10 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
         <v>8</v>
@@ -4254,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4266,7 +4333,7 @@
         <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB21" t="n">
         <v>11</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F22" t="n">
         <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>0.732</v>
+        <v>0.729</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,7 +4386,7 @@
         <v>38.1</v>
       </c>
       <c r="J22" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K22" t="n">
         <v>0.481</v>
@@ -4328,19 +4395,19 @@
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N22" t="n">
         <v>0.377</v>
       </c>
       <c r="O22" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="P22" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.826</v>
+        <v>0.827</v>
       </c>
       <c r="R22" t="n">
         <v>10.4</v>
@@ -4355,10 +4422,10 @@
         <v>21.5</v>
       </c>
       <c r="V22" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
         <v>7.5</v>
@@ -4367,19 +4434,19 @@
         <v>4.1</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.2</v>
+        <v>106.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4391,7 +4458,7 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4403,10 +4470,10 @@
         <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN22" t="n">
         <v>5</v>
@@ -4424,10 +4491,10 @@
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>20</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4573,13 +4640,13 @@
         <v>29</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK23" t="n">
         <v>12</v>
@@ -4588,7 +4655,7 @@
         <v>21</v>
       </c>
       <c r="AM23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -4665,31 +4732,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
         <v>42</v>
       </c>
       <c r="G24" t="n">
-        <v>0.391</v>
+        <v>0.382</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J24" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M24" t="n">
         <v>17.4</v>
@@ -4701,22 +4768,22 @@
         <v>11.9</v>
       </c>
       <c r="P24" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0.718</v>
       </c>
       <c r="R24" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S24" t="n">
         <v>30.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U24" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V24" t="n">
         <v>13.2</v>
@@ -4728,22 +4795,22 @@
         <v>4.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4758,13 +4825,13 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4785,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
         <v>16</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4815,7 +4882,7 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G25" t="n">
-        <v>0.324</v>
+        <v>0.329</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J25" t="n">
-        <v>84.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.44</v>
@@ -4874,7 +4941,7 @@
         <v>5.6</v>
       </c>
       <c r="M25" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N25" t="n">
         <v>0.321</v>
@@ -4886,25 +4953,25 @@
         <v>19.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R25" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S25" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T25" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U25" t="n">
         <v>22.1</v>
       </c>
       <c r="V25" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W25" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X25" t="n">
         <v>5.3</v>
@@ -4919,19 +4986,19 @@
         <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="AC25" t="n">
         <v>-6.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
         <v>27</v>
@@ -4967,10 +5034,10 @@
         <v>23</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -4988,7 +5055,7 @@
         <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ25" t="n">
         <v>22</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -5029,61 +5096,61 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" t="n">
-        <v>0.471</v>
+        <v>0.478</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J26" t="n">
         <v>82.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>23.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.356</v>
+        <v>0.355</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P26" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="Q26" t="n">
         <v>0.78</v>
       </c>
       <c r="R26" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S26" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T26" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U26" t="n">
         <v>21.7</v>
       </c>
       <c r="V26" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W26" t="n">
         <v>6.8</v>
@@ -5101,25 +5168,25 @@
         <v>18.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.4</v>
+        <v>-1.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5128,7 +5195,7 @@
         <v>11</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5152,7 +5219,7 @@
         <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT26" t="n">
         <v>18</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" t="n">
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>0.352</v>
+        <v>0.357</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5229,7 +5296,7 @@
         <v>37.4</v>
       </c>
       <c r="J27" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.447</v>
@@ -5241,16 +5308,16 @@
         <v>20</v>
       </c>
       <c r="N27" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O27" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="P27" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R27" t="n">
         <v>11.4</v>
@@ -5274,22 +5341,22 @@
         <v>4.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.1</v>
+        <v>-5</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5301,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>12</v>
@@ -5313,7 +5380,7 @@
         <v>16</v>
       </c>
       <c r="AL27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM27" t="n">
         <v>12</v>
@@ -5322,19 +5389,19 @@
         <v>9</v>
       </c>
       <c r="AO27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT27" t="n">
         <v>26</v>
@@ -5346,7 +5413,7 @@
         <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5355,7 +5422,7 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E28" t="n">
         <v>53</v>
       </c>
       <c r="F28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.757</v>
+        <v>0.768</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>39.5</v>
+        <v>39.6</v>
       </c>
       <c r="J28" t="n">
         <v>81.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.487</v>
+        <v>0.488</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
@@ -5423,7 +5490,7 @@
         <v>21.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.381</v>
+        <v>0.379</v>
       </c>
       <c r="O28" t="n">
         <v>16.9</v>
@@ -5432,7 +5499,7 @@
         <v>21.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R28" t="n">
         <v>8</v>
@@ -5441,10 +5508,10 @@
         <v>33.1</v>
       </c>
       <c r="T28" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U28" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
@@ -5456,7 +5523,7 @@
         <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
         <v>17.4</v>
@@ -5465,13 +5532,13 @@
         <v>19.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.3</v>
+        <v>104.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5516,7 +5583,7 @@
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT28" t="n">
         <v>22</v>
@@ -5546,7 +5613,7 @@
         <v>4</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
         <v>21</v>
@@ -5680,13 +5747,13 @@
         <v>14</v>
       </c>
       <c r="AM29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN29" t="n">
         <v>25</v>
       </c>
       <c r="AO29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" t="n">
         <v>34</v>
       </c>
       <c r="F30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G30" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H30" t="n">
         <v>48.6</v>
       </c>
       <c r="I30" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J30" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
@@ -5802,16 +5869,16 @@
         <v>12.4</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T30" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U30" t="n">
         <v>22.4</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
         <v>8.300000000000001</v>
@@ -5829,13 +5896,13 @@
         <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>97.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="AC30" t="n">
         <v>-0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5850,13 +5917,13 @@
         <v>5</v>
       </c>
       <c r="AI30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ30" t="n">
         <v>14</v>
       </c>
       <c r="AK30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="n">
         <v>25</v>
@@ -5877,10 +5944,10 @@
         <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
@@ -5889,10 +5956,10 @@
         <v>13</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-2.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>22</v>
       </c>
       <c r="AF31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG31" t="n">
         <v>22</v>
@@ -6032,13 +6099,13 @@
         <v>8</v>
       </c>
       <c r="AI31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>18</v>
@@ -6059,7 +6126,7 @@
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -6074,7 +6141,7 @@
         <v>27</v>
       </c>
       <c r="AW31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX31" t="n">
         <v>23</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-24-2012-13</t>
+          <t>2013-03-24</t>
         </is>
       </c>
     </row>
